--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2021/American_Aircraft_Cumulative_Statistics_2021.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2021/American_Aircraft_Cumulative_Statistics_2021.xlsx
@@ -13,36 +13,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="24">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -124,10 +130,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="true"/>
+    <col min="1" max="1" width="9.28515625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -147,40 +153,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -188,40 +194,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>2491632951</v>
+        <v>12776231245</v>
       </c>
       <c r="C2" s="0">
-        <v>3429855150</v>
+        <v>16234917761</v>
       </c>
       <c r="D2" s="0">
-        <v>417257</v>
+        <v>342870</v>
       </c>
       <c r="E2" s="0">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="F2" s="0">
-        <v>25908</v>
+        <v>155420</v>
       </c>
       <c r="G2" s="0">
-        <v>3.1499999999999999</v>
+        <v>3.2799999999999998</v>
       </c>
       <c r="H2" s="0">
-        <v>7.8399999999999999</v>
+        <v>7.6299999999999999</v>
       </c>
       <c r="I2" s="0">
-        <v>72.650000000000006</v>
+        <v>78.700000000000003</v>
       </c>
       <c r="J2" s="0">
-        <v>883</v>
+        <v>816</v>
       </c>
       <c r="K2" s="0">
-        <v>5832</v>
+        <v>4276.6400000000003</v>
       </c>
       <c r="L2" s="0">
-        <v>38.880000000000003</v>
+        <v>33.409999999999997</v>
       </c>
       <c r="M2" s="0">
-        <v>0.11</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -229,40 +235,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>8948333478</v>
+        <v>5549372526</v>
       </c>
       <c r="C3" s="0">
-        <v>12533603874</v>
+        <v>7014574577</v>
       </c>
       <c r="D3" s="0">
-        <v>504573</v>
+        <v>400604</v>
       </c>
       <c r="E3" s="0">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="F3" s="0">
-        <v>77210</v>
+        <v>62422</v>
       </c>
       <c r="G3" s="0">
-        <v>3.1099999999999999</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="H3" s="0">
-        <v>7.2199999999999998</v>
+        <v>7.75</v>
       </c>
       <c r="I3" s="0">
-        <v>71.390000000000001</v>
+        <v>79.109999999999999</v>
       </c>
       <c r="J3" s="0">
-        <v>888</v>
+        <v>749</v>
       </c>
       <c r="K3" s="0">
-        <v>4075</v>
+        <v>4932.8900000000003</v>
       </c>
       <c r="L3" s="0">
-        <v>22.289999999999999</v>
+        <v>32.890000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -270,40 +276,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>5549372526</v>
+        <v>38826580259</v>
       </c>
       <c r="C4" s="0">
-        <v>7014574577</v>
+        <v>47410616694</v>
       </c>
       <c r="D4" s="0">
-        <v>400604</v>
+        <v>602958</v>
       </c>
       <c r="E4" s="0">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="F4" s="0">
-        <v>62422</v>
+        <v>229465</v>
       </c>
       <c r="G4" s="0">
-        <v>3.5600000000000001</v>
+        <v>2.9199999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>7.75</v>
+        <v>8.6600000000000001</v>
       </c>
       <c r="I4" s="0">
-        <v>79.109999999999999</v>
+        <v>81.890000000000001</v>
       </c>
       <c r="J4" s="0">
-        <v>749</v>
+        <v>1145</v>
       </c>
       <c r="K4" s="0">
-        <v>4933</v>
+        <v>6200.0299999999997</v>
       </c>
       <c r="L4" s="0">
-        <v>32.890000000000001</v>
+        <v>34.210000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="5">
@@ -311,40 +317,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>6443009126</v>
+        <v>8657819547</v>
       </c>
       <c r="C5" s="0">
-        <v>8918704215</v>
+        <v>11262067427</v>
       </c>
       <c r="D5" s="0">
-        <v>451809</v>
+        <v>887476</v>
       </c>
       <c r="E5" s="0">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="F5" s="0">
-        <v>70425</v>
+        <v>32151</v>
       </c>
       <c r="G5" s="0">
-        <v>3.5699999999999998</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H5" s="0">
-        <v>7.9100000000000001</v>
+        <v>10.539999999999999</v>
       </c>
       <c r="I5" s="0">
-        <v>72.239999999999995</v>
+        <v>76.879999999999995</v>
       </c>
       <c r="J5" s="0">
-        <v>807</v>
+        <v>1787</v>
       </c>
       <c r="K5" s="0">
-        <v>4930</v>
+        <v>6628.2700000000004</v>
       </c>
       <c r="L5" s="0">
-        <v>31.41</v>
+        <v>33.82</v>
       </c>
       <c r="M5" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -352,40 +358,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>2942555611</v>
+        <v>39923231142</v>
       </c>
       <c r="C6" s="0">
-        <v>3821264460</v>
+        <v>50601182323</v>
       </c>
       <c r="D6" s="0">
-        <v>634762</v>
+        <v>538826</v>
       </c>
       <c r="E6" s="0">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="F6" s="0">
-        <v>22346</v>
+        <v>291391</v>
       </c>
       <c r="G6" s="0">
-        <v>3.71</v>
+        <v>3.1000000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>9.6099999999999994</v>
+        <v>8.4299999999999997</v>
       </c>
       <c r="I6" s="0">
-        <v>77</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="J6" s="0">
-        <v>942</v>
+        <v>1010</v>
       </c>
       <c r="K6" s="0">
-        <v>4203</v>
+        <v>5537.4300000000003</v>
       </c>
       <c r="L6" s="0">
-        <v>23.170000000000002</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="M6" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="7">
@@ -393,40 +399,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>18881095357</v>
+        <v>6023614369</v>
       </c>
       <c r="C7" s="0">
-        <v>25247743908</v>
+        <v>7600097952</v>
       </c>
       <c r="D7" s="0">
-        <v>532092</v>
+        <v>505326</v>
       </c>
       <c r="E7" s="0">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F7" s="0">
-        <v>120816</v>
+        <v>39462</v>
       </c>
       <c r="G7" s="0">
-        <v>2.5499999999999998</v>
+        <v>2.6200000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>8.3800000000000008</v>
+        <v>7.6799999999999997</v>
       </c>
       <c r="I7" s="0">
-        <v>74.780000000000001</v>
+        <v>79.260000000000005</v>
       </c>
       <c r="J7" s="0">
-        <v>1308</v>
+        <v>1120</v>
       </c>
       <c r="K7" s="0">
-        <v>5430</v>
+        <v>5320.4899999999998</v>
       </c>
       <c r="L7" s="0">
-        <v>33.990000000000002</v>
+        <v>30.93</v>
       </c>
       <c r="M7" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -434,40 +440,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>12731865011</v>
+        <v>4588428247</v>
       </c>
       <c r="C8" s="0">
-        <v>16295342566</v>
+        <v>7468238984</v>
       </c>
       <c r="D8" s="0">
-        <v>657335</v>
+        <v>870424</v>
       </c>
       <c r="E8" s="0">
-        <v>182</v>
+        <v>228</v>
       </c>
       <c r="F8" s="0">
-        <v>90691</v>
+        <v>13150</v>
       </c>
       <c r="G8" s="0">
-        <v>3.6600000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="H8" s="0">
-        <v>9.5099999999999998</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="I8" s="0">
-        <v>78.129999999999995</v>
+        <v>61.439999999999998</v>
       </c>
       <c r="J8" s="0">
-        <v>987</v>
+        <v>2605</v>
       </c>
       <c r="K8" s="0">
-        <v>3995</v>
+        <v>9786.1100000000006</v>
       </c>
       <c r="L8" s="0">
-        <v>21.949999999999999</v>
+        <v>44.710000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -475,40 +481,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>8066452746</v>
+        <v>4556173165</v>
       </c>
       <c r="C9" s="0">
-        <v>10540240950</v>
+        <v>9530006456</v>
       </c>
       <c r="D9" s="0">
-        <v>300806</v>
+        <v>1186800</v>
       </c>
       <c r="E9" s="0">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="F9" s="0">
-        <v>70653</v>
+        <v>9416</v>
       </c>
       <c r="G9" s="0">
-        <v>2.02</v>
+        <v>1.1699999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>5.3300000000000001</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="I9" s="0">
-        <v>76.530000000000001</v>
+        <v>47.810000000000002</v>
       </c>
       <c r="J9" s="0">
-        <v>995</v>
+        <v>3911</v>
       </c>
       <c r="K9" s="0">
-        <v>5522</v>
+        <v>11757.790000000001</v>
       </c>
       <c r="L9" s="0">
-        <v>36.810000000000002</v>
+        <v>45.420000000000002</v>
       </c>
       <c r="M9" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.090999999999999998</v>
       </c>
     </row>
     <row r="10">
@@ -516,40 +522,122 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>66054316806</v>
+        <v>10512067774</v>
       </c>
       <c r="C10" s="0">
-        <v>87801329700</v>
+        <v>16575561222</v>
       </c>
       <c r="D10" s="0">
-        <v>478195</v>
+        <v>981965</v>
       </c>
       <c r="E10" s="0">
-        <v>164</v>
+        <v>268</v>
       </c>
       <c r="F10" s="0">
-        <v>540471</v>
+        <v>22902</v>
       </c>
       <c r="G10" s="0">
-        <v>2.9399999999999999</v>
+        <v>1.3600000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>7.7000000000000002</v>
+        <v>7.9299999999999997</v>
       </c>
       <c r="I10" s="0">
-        <v>75.230000000000004</v>
+        <v>63.420000000000002</v>
       </c>
       <c r="J10" s="0">
-        <v>988</v>
+        <v>2740</v>
       </c>
       <c r="K10" s="0">
-        <v>4896</v>
+        <v>12015.99</v>
       </c>
       <c r="L10" s="0">
-        <v>29.800000000000001</v>
+        <v>45.420000000000002</v>
       </c>
       <c r="M10" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.097000000000000003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>5084926083</v>
+      </c>
+      <c r="C11" s="0">
+        <v>8436785934</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1157309</v>
+      </c>
+      <c r="E11" s="0">
+        <v>295</v>
+      </c>
+      <c r="F11" s="0">
+        <v>9160</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1.26</v>
+      </c>
+      <c r="H11" s="0">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="I11" s="0">
+        <v>60.270000000000003</v>
+      </c>
+      <c r="J11" s="0">
+        <v>3191</v>
+      </c>
+      <c r="K11" s="0">
+        <v>13818.629999999999</v>
+      </c>
+      <c r="L11" s="0">
+        <v>47.729999999999997</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>136498444357</v>
+      </c>
+      <c r="C12" s="0">
+        <v>182134049330</v>
+      </c>
+      <c r="D12" s="0">
+        <v>595384</v>
+      </c>
+      <c r="E12" s="0">
+        <v>172</v>
+      </c>
+      <c r="F12" s="0">
+        <v>864939</v>
+      </c>
+      <c r="G12" s="0">
+        <v>2.8300000000000001</v>
+      </c>
+      <c r="H12" s="0">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="I12" s="0">
+        <v>74.939999999999998</v>
+      </c>
+      <c r="J12" s="0">
+        <v>1151</v>
+      </c>
+      <c r="K12" s="0">
+        <v>6387.2399999999998</v>
+      </c>
+      <c r="L12" s="0">
+        <v>35.520000000000003</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.089999999999999997</v>
       </c>
     </row>
   </sheetData>
